--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_a_2018_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_a_2018_magallanes.xlsx
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 10:45</t>
+    <t xml:space="preserve">2026-10-01 23:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_a_2018_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_a_2018_magallanes.xlsx
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:13</t>
+    <t xml:space="preserve">2026-10-05 19:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
